--- a/Data/FlightPlan/FPL_27SEP26.xlsx
+++ b/Data/FlightPlan/FPL_27SEP26.xlsx
@@ -350,15 +350,30 @@
     <t>13:25</t>
   </si>
   <si>
+    <t>17:01</t>
+  </si>
+  <si>
     <t>17:00</t>
   </si>
   <si>
     <t>19:10</t>
   </si>
   <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
     <t>21:50</t>
   </si>
   <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
     <t>VN-A523</t>
   </si>
   <si>
@@ -431,9 +446,6 @@
     <t>16:12</t>
   </si>
   <si>
-    <t>18:00</t>
-  </si>
-  <si>
     <t>19:00</t>
   </si>
   <si>
@@ -449,7 +461,7 @@
     <t>20:05</t>
   </si>
   <si>
-    <t>21:21</t>
+    <t>21:35</t>
   </si>
   <si>
     <t>01:20</t>
@@ -533,9 +545,6 @@
     <t>18:40</t>
   </si>
   <si>
-    <t>20:30</t>
-  </si>
-  <si>
     <t>21:00</t>
   </si>
   <si>
@@ -557,12 +566,15 @@
     <t>DLI</t>
   </si>
   <si>
-    <t>16:01</t>
-  </si>
-  <si>
     <t>22:10</t>
   </si>
   <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
     <t>23:10</t>
   </si>
   <si>
@@ -692,9 +704,6 @@
     <t>09:04</t>
   </si>
   <si>
-    <t>17:01</t>
-  </si>
-  <si>
     <t>23:05</t>
   </si>
   <si>
@@ -734,306 +743,306 @@
     <t>15:00</t>
   </si>
   <si>
+    <t>22:21</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>02:25</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>11:06</t>
+  </si>
+  <si>
+    <t>HGH</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>15:29</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>11:49</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>15:16</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>08:07</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>10:09</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>12:16</t>
+  </si>
+  <si>
+    <t>14:02</t>
+  </si>
+  <si>
+    <t>16:07</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>14:11</t>
+  </si>
+  <si>
+    <t>18:29</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>13:47</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>09:38</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>12:13</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>15:12</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>11:04</t>
+  </si>
+  <si>
+    <t>14:17</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>16:29</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:45</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>11:01</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>15:36</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:12</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>10:57</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>15:34</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
     <t>22:05</t>
   </si>
   <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>02:25</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>11:06</t>
-  </si>
-  <si>
-    <t>HGH</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>15:29</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>11:49</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>15:16</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>08:07</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>10:09</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>12:16</t>
-  </si>
-  <si>
-    <t>14:02</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>14:11</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>13:47</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>09:38</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>12:13</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>15:12</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>11:04</t>
-  </si>
-  <si>
-    <t>14:17</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:45</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>11:01</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>15:36</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:12</t>
-  </si>
-  <si>
-    <t>09:01</t>
-  </si>
-  <si>
-    <t>10:57</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>12:46</t>
-  </si>
-  <si>
-    <t>15:34</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
     <t>VN-A640</t>
   </si>
   <si>
@@ -1142,9 +1151,15 @@
     <t>16:35</t>
   </si>
   <si>
+    <t>16:53</t>
+  </si>
+  <si>
     <t>VN-A650</t>
   </si>
   <si>
+    <t>17:17</t>
+  </si>
+  <si>
     <t>VCL</t>
   </si>
   <si>
@@ -1199,15 +1214,21 @@
     <t>10:49</t>
   </si>
   <si>
-    <t>16:06</t>
+    <t>16:08</t>
   </si>
   <si>
     <t>17:35</t>
   </si>
   <si>
+    <t>20:40</t>
+  </si>
+  <si>
     <t>VN-A658</t>
   </si>
   <si>
+    <t>16:32</t>
+  </si>
+  <si>
     <t>VN-A661</t>
   </si>
   <si>
@@ -1223,9 +1244,6 @@
     <t>PVG</t>
   </si>
   <si>
-    <t>20:00</t>
-  </si>
-  <si>
     <t>02:15</t>
   </si>
   <si>
@@ -1292,9 +1310,6 @@
     <t>08:15</t>
   </si>
   <si>
-    <t>16:07</t>
-  </si>
-  <si>
     <t>23:55</t>
   </si>
   <si>
@@ -1409,9 +1424,6 @@
     <t>09:55</t>
   </si>
   <si>
-    <t>20:40</t>
-  </si>
-  <si>
     <t>VN-A683</t>
   </si>
   <si>
@@ -1478,6 +1490,9 @@
     <t>VN-A698</t>
   </si>
   <si>
+    <t>16:19</t>
+  </si>
+  <si>
     <t>23:25</t>
   </si>
   <si>
@@ -1562,7 +1577,7 @@
     <t>Total Record(s): 381</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 27, 2026 15:01</t>
+    <t xml:space="preserve">Generated on  Sep 27, 2026 15:21</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3282,7 +3297,9 @@
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
-      <c r="M43" s="7"/>
+      <c t="s" r="M43" s="7">
+        <v>113</v>
+      </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c t="s" r="A44" s="6">
@@ -3308,14 +3325,18 @@
         <v>51</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>114</v>
-      </c>
-      <c r="K44" s="7"/>
+        <v>115</v>
+      </c>
+      <c t="s" r="K44" s="7">
+        <v>116</v>
+      </c>
       <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
+      <c t="s" r="M44" s="7">
+        <v>117</v>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c t="s" r="A45" s="6">
@@ -3344,11 +3365,15 @@
         <v>44</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>115</v>
-      </c>
-      <c r="K45" s="7"/>
+        <v>118</v>
+      </c>
+      <c t="s" r="K45" s="7">
+        <v>119</v>
+      </c>
       <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
+      <c t="s" r="M45" s="7">
+        <v>120</v>
+      </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="6"/>
@@ -3377,13 +3402,13 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c t="s" r="H47" s="8">
         <v>21</v>
@@ -3392,12 +3417,12 @@
         <v>53</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c t="s" r="M47" s="7">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -3412,7 +3437,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3424,17 +3449,17 @@
         <v>70</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c t="s" r="K48" s="7">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L48" s="7"/>
       <c t="s" r="M48" s="7">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
@@ -3449,7 +3474,7 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -3464,7 +3489,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3497,7 +3522,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3509,15 +3534,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
       <c t="s" r="M51" s="7">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -3532,7 +3557,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3547,12 +3572,12 @@
         <v>26</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c t="s" r="M52" s="7">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
@@ -3567,7 +3592,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3579,17 +3604,17 @@
         <v>58</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c t="s" r="K53" s="7">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="L53" s="7"/>
       <c t="s" r="M53" s="7">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
@@ -3604,7 +3629,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3616,7 +3641,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c t="s" r="J54" s="7">
         <v>45</v>
@@ -3648,17 +3673,17 @@
         <v>3524</v>
       </c>
       <c t="s" r="C56" s="7">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c t="s" r="H56" s="8">
         <v>50</v>
@@ -3667,12 +3692,12 @@
         <v>20</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
       <c t="s" r="M56" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -3683,11 +3708,11 @@
         <v>3524</v>
       </c>
       <c t="s" r="C57" s="7">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3699,15 +3724,15 @@
         <v>70</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
       <c t="s" r="M57" s="7">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
@@ -3722,7 +3747,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3734,10 +3759,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3770,7 +3795,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3779,18 +3804,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c t="s" r="M60" s="7">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -3805,27 +3830,27 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G61" s="8">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c t="s" r="H61" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
       <c t="s" r="M61" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -3840,7 +3865,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3852,10 +3877,10 @@
         <v>103</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3888,7 +3913,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3908,7 +3933,7 @@
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c t="s" r="M64" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
@@ -3923,7 +3948,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3938,12 +3963,12 @@
         <v>91</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
       <c t="s" r="M65" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -3958,7 +3983,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3970,7 +3995,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c t="s" r="J66" s="7">
         <v>94</v>
@@ -3978,7 +4003,7 @@
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c t="s" r="M66" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -3993,7 +4018,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -4005,17 +4030,17 @@
         <v>50</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="K67" s="7">
         <v>79</v>
       </c>
       <c r="L67" s="7"/>
       <c t="s" r="M67" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
@@ -4030,7 +4055,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -4045,7 +4070,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c t="s" r="K68" s="7">
         <v>81</v>
@@ -4067,7 +4092,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -4079,7 +4104,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c t="s" r="J69" s="7">
         <v>29</v>
@@ -4100,7 +4125,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -4112,10 +4137,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -4133,7 +4158,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -4145,10 +4170,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -4181,7 +4206,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -4196,12 +4221,12 @@
         <v>71</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c t="s" r="M73" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -4216,7 +4241,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -4225,10 +4250,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J74" s="7">
         <v>37</v>
@@ -4236,7 +4261,7 @@
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -4251,19 +4276,19 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="H75" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="J75" s="7">
         <v>20</v>
@@ -4271,7 +4296,7 @@
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4286,7 +4311,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4306,7 +4331,7 @@
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4321,7 +4346,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4330,10 +4355,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H77" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="J77" s="7">
         <v>83</v>
@@ -4341,7 +4366,7 @@
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c t="s" r="M77" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -4356,19 +4381,19 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="H78" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c t="s" r="J78" s="7">
         <v>29</v>
@@ -4389,7 +4414,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4401,10 +4426,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>174</v>
+        <v>119</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -4422,7 +4447,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4434,10 +4459,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4470,27 +4495,27 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G82" s="8">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c t="s" r="H82" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
       <c t="s" r="M82" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -4505,7 +4530,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4514,7 +4539,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H83" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="I83" s="7">
         <v>26</v>
@@ -4525,7 +4550,7 @@
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>182</v>
+        <v>65</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4540,13 +4565,13 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G84" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="H84" s="8">
         <v>50</v>
@@ -4573,7 +4598,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4585,14 +4610,18 @@
         <v>70</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>183</v>
-      </c>
-      <c r="K85" s="7"/>
+        <v>185</v>
+      </c>
+      <c t="s" r="K85" s="7">
+        <v>186</v>
+      </c>
       <c r="L85" s="7"/>
-      <c r="M85" s="7"/>
+      <c t="s" r="M85" s="7">
+        <v>187</v>
+      </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c t="s" r="A86" s="6">
@@ -4606,7 +4635,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4618,7 +4647,7 @@
         <v>90</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c t="s" r="J86" s="7">
         <v>107</v>
@@ -4654,7 +4683,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4666,7 +4695,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c t="s" r="J88" s="7">
         <v>111</v>
@@ -4674,7 +4703,7 @@
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -4689,7 +4718,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4701,7 +4730,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c t="s" r="J89" s="7">
         <v>79</v>
@@ -4709,7 +4738,7 @@
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -4724,7 +4753,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4736,15 +4765,15 @@
         <v>70</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -4759,7 +4788,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4771,10 +4800,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4807,7 +4836,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4816,18 +4845,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="I93" s="7">
         <v>107</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -4842,19 +4871,19 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c t="s" r="J94" s="7">
         <v>55</v>
@@ -4862,7 +4891,7 @@
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -4877,7 +4906,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4886,7 +4915,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c t="s" r="I95" s="7">
         <v>19</v>
@@ -4897,7 +4926,7 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -4912,22 +4941,22 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c t="s" r="H96" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4947,7 +4976,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4956,10 +4985,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c t="s" r="J97" s="7">
         <v>66</v>
@@ -4980,13 +5009,13 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="H98" s="8">
         <v>21</v>
@@ -4995,7 +5024,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -5013,7 +5042,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -5022,13 +5051,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -5046,22 +5075,22 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c t="s" r="H100" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -5094,7 +5123,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5109,12 +5138,12 @@
         <v>56</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -5129,7 +5158,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5141,10 +5170,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -5162,7 +5191,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5171,13 +5200,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -5195,22 +5224,22 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -5243,7 +5272,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5255,15 +5284,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -5278,7 +5307,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5290,7 +5319,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>57</v>
@@ -5313,7 +5342,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5325,15 +5354,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c t="s" r="M109" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
@@ -5348,7 +5377,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5381,7 +5410,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5396,7 +5425,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -5414,7 +5443,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5426,10 +5455,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5462,7 +5491,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5474,15 +5503,15 @@
         <v>70</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c t="s" r="M114" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -5497,7 +5526,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5509,7 +5538,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="J115" s="7">
         <v>111</v>
@@ -5532,7 +5561,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5554,7 +5583,7 @@
       </c>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5569,7 +5598,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5584,14 +5613,14 @@
         <v>26</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c t="s" r="K117" s="7">
         <v>96</v>
       </c>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>227</v>
+        <v>133</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5606,7 +5635,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5618,10 +5647,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5654,7 +5683,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5669,14 +5698,14 @@
         <v>40</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c t="s" r="K120" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5691,7 +5720,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5703,10 +5732,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5724,7 +5753,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5736,7 +5765,7 @@
         <v>80</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>44</v>
@@ -5757,7 +5786,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5769,10 +5798,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5805,7 +5834,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5817,7 +5846,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c t="s" r="J125" s="7">
         <v>38</v>
@@ -5842,7 +5871,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5854,10 +5883,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5890,7 +5919,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5925,7 +5954,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5937,17 +5966,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c t="s" r="K129" s="7">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -5962,7 +5991,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5974,17 +6003,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c t="s" r="K130" s="7">
         <v>67</v>
       </c>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -6010,11 +6039,11 @@
         <v>7621</v>
       </c>
       <c t="s" r="C132" s="7">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6029,12 +6058,12 @@
         <v>73</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -6049,7 +6078,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6058,13 +6087,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>249</v>
+        <v>186</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -6082,22 +6111,22 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -6115,7 +6144,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6127,7 +6156,7 @@
         <v>90</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>74</v>
@@ -6163,27 +6192,27 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6198,7 +6227,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6213,12 +6242,12 @@
         <v>79</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6229,11 +6258,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C139" s="7">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6245,10 +6274,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -6262,11 +6291,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6275,13 +6304,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I140" s="7">
         <v>101</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -6314,7 +6343,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6326,15 +6355,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6349,7 +6378,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6358,18 +6387,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="I143" s="7">
         <v>60</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6384,19 +6413,19 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>101</v>
@@ -6417,7 +6446,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6426,13 +6455,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6465,7 +6494,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6474,10 +6503,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>78</v>
@@ -6500,13 +6529,13 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>21</v>
@@ -6515,12 +6544,12 @@
         <v>60</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6535,7 +6564,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6544,13 +6573,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6568,22 +6597,22 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6601,7 +6630,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6613,10 +6642,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6649,27 +6678,27 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6684,7 +6713,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6693,10 +6722,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>31</v>
@@ -6717,13 +6746,13 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>21</v>
@@ -6732,7 +6761,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6750,7 +6779,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6759,7 +6788,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="I156" s="7">
         <v>104</v>
@@ -6798,7 +6827,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6807,10 +6836,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>77</v>
@@ -6818,7 +6847,7 @@
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6833,13 +6862,13 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>50</v>
@@ -6848,12 +6877,12 @@
         <v>78</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -6868,7 +6897,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6883,7 +6912,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6901,7 +6930,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6913,10 +6942,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6934,7 +6963,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6943,13 +6972,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>280</v>
+        <v>120</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6967,13 +6996,13 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>50</v>
@@ -7062,10 +7091,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -7130,7 +7159,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J168" s="7">
         <v>290</v>
@@ -7208,7 +7237,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I171" s="7">
         <v>294</v>
@@ -7240,7 +7269,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>21</v>
@@ -7249,7 +7278,7 @@
         <v>296</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -7281,10 +7310,10 @@
         <v>298</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -7316,10 +7345,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -7351,7 +7380,7 @@
         <v>70</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>27</v>
@@ -7359,7 +7388,7 @@
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>82</v>
+        <v>301</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7389,7 +7418,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7419,10 +7448,10 @@
         <v>298</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7452,10 +7481,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7488,7 +7517,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7497,18 +7526,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7523,13 +7552,13 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>50</v>
@@ -7538,12 +7567,12 @@
         <v>77</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7558,7 +7587,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7576,11 +7605,11 @@
         <v>66</v>
       </c>
       <c t="s" r="K182" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>289</v>
+        <v>308</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7595,7 +7624,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7607,7 +7636,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>87</v>
@@ -7628,7 +7657,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7640,10 +7669,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7676,7 +7705,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7685,18 +7714,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H186" s="8">
+        <v>173</v>
+      </c>
+      <c t="s" r="I186" s="7">
+        <v>165</v>
+      </c>
+      <c t="s" r="J186" s="7">
         <v>169</v>
-      </c>
-      <c t="s" r="I186" s="7">
-        <v>161</v>
-      </c>
-      <c t="s" r="J186" s="7">
-        <v>165</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -7711,22 +7740,22 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7746,7 +7775,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7761,12 +7790,12 @@
         <v>286</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7781,7 +7810,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7793,15 +7822,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -7816,7 +7845,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7828,10 +7857,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7849,7 +7878,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7861,10 +7890,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>311</v>
+        <v>187</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7882,7 +7911,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7894,10 +7923,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7930,7 +7959,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7950,7 +7979,7 @@
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -7965,7 +7994,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7977,7 +8006,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>22</v>
@@ -7985,7 +8014,7 @@
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8000,7 +8029,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8012,7 +8041,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>96</v>
@@ -8020,7 +8049,7 @@
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8035,7 +8064,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8044,7 +8073,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="I197" s="7">
         <v>83</v>
@@ -8068,13 +8097,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>50</v>
@@ -8083,7 +8112,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -8116,7 +8145,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8136,7 +8165,7 @@
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8151,7 +8180,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8163,15 +8192,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8186,7 +8215,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8201,14 +8230,14 @@
         <v>23</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="K202" s="7">
         <v>81</v>
       </c>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>85</v>
+        <v>325</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8223,7 +8252,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8235,7 +8264,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>100</v>
@@ -8256,7 +8285,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8268,10 +8297,10 @@
         <v>80</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -8289,7 +8318,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8301,10 +8330,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -8337,7 +8366,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8352,7 +8381,7 @@
         <v>285</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8372,7 +8401,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8384,7 +8413,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>20</v>
@@ -8392,7 +8421,7 @@
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8407,7 +8436,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8427,7 +8456,7 @@
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8442,7 +8471,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8460,11 +8489,11 @@
         <v>40</v>
       </c>
       <c t="s" r="K210" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8479,7 +8508,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8488,13 +8517,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="I211" s="7">
         <v>83</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8512,19 +8541,19 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>101</v>
@@ -8560,7 +8589,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8572,15 +8601,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8595,7 +8624,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8610,12 +8639,12 @@
         <v>285</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8630,7 +8659,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8642,15 +8671,15 @@
         <v>298</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8665,7 +8694,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8680,14 +8709,14 @@
         <v>92</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c t="s" r="K217" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8702,7 +8731,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8720,11 +8749,11 @@
         <v>81</v>
       </c>
       <c t="s" r="K218" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -8739,7 +8768,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8757,11 +8786,11 @@
         <v>84</v>
       </c>
       <c t="s" r="K219" s="7">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -8776,7 +8805,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8788,10 +8817,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8809,7 +8838,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8821,10 +8850,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>241</v>
+        <v>343</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8857,7 +8886,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8866,7 +8895,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="I223" s="7">
         <v>296</v>
@@ -8892,13 +8921,13 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>50</v>
@@ -8907,12 +8936,12 @@
         <v>26</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8927,7 +8956,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8939,17 +8968,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c t="s" r="K225" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -8964,7 +8993,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8973,10 +9002,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>281</v>
@@ -8997,22 +9026,22 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -9045,7 +9074,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9057,10 +9086,10 @@
         <v>80</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -9080,7 +9109,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9092,7 +9121,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>96</v>
@@ -9100,7 +9129,7 @@
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9130,7 +9159,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9150,7 +9179,7 @@
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9165,7 +9194,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9177,7 +9206,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>60</v>
@@ -9185,7 +9214,7 @@
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9200,7 +9229,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9212,7 +9241,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>98</v>
@@ -9220,7 +9249,7 @@
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9235,7 +9264,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9250,7 +9279,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -9268,7 +9297,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9280,10 +9309,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -9301,7 +9330,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9313,10 +9342,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9349,7 +9378,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9369,7 +9398,7 @@
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9384,7 +9413,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9393,10 +9422,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>94</v>
@@ -9404,7 +9433,7 @@
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9419,13 +9448,13 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>70</v>
@@ -9434,12 +9463,12 @@
         <v>79</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9454,7 +9483,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9463,7 +9492,7 @@
         <v>70</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="I242" s="7">
         <v>98</v>
@@ -9487,19 +9516,19 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c t="s" r="J243" s="7">
         <v>87</v>
@@ -9535,7 +9564,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9570,7 +9599,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9579,18 +9608,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -9605,22 +9634,22 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9638,7 +9667,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9653,7 +9682,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9686,7 +9715,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9695,18 +9724,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -9721,27 +9750,27 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9756,7 +9785,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9765,13 +9794,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="I252" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9791,13 +9820,13 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="H253" s="8">
         <v>50</v>
@@ -9811,7 +9840,7 @@
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -9826,7 +9855,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9838,10 +9867,10 @@
         <v>70</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9859,7 +9888,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9874,7 +9903,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9907,7 +9936,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9919,15 +9948,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -9942,7 +9971,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9954,15 +9983,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -9977,7 +10006,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9986,18 +10015,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>60</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10012,22 +10041,22 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -10045,7 +10074,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10054,13 +10083,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -10093,7 +10122,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10102,18 +10131,18 @@
         <v>58</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c t="s" r="I263" s="7">
         <v>94</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10128,13 +10157,13 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>58</v>
@@ -10143,11 +10172,13 @@
         <v>27</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
-      <c r="M264" s="7"/>
+      <c t="s" r="M264" s="7">
+        <v>380</v>
+      </c>
     </row>
     <row r="265" ht="15" customHeight="1">
       <c r="A265" s="6"/>
@@ -10176,7 +10207,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
@@ -10185,18 +10216,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="I266" s="7">
         <v>72</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10211,19 +10242,19 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>111</v>
@@ -10231,7 +10262,7 @@
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10246,7 +10277,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -10281,7 +10312,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -10293,17 +10324,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c t="s" r="K269" s="7">
         <v>81</v>
       </c>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>113</v>
+        <v>382</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10318,7 +10349,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -10327,13 +10358,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c t="s" r="I270" s="7">
         <v>289</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -10351,22 +10382,22 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -10399,7 +10430,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10414,12 +10445,12 @@
         <v>53</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10434,7 +10465,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10454,7 +10485,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10469,7 +10500,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10481,15 +10512,15 @@
         <v>51</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10504,7 +10535,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10516,10 +10547,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10552,7 +10583,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10561,18 +10592,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10587,13 +10618,13 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>21</v>
@@ -10607,7 +10638,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10622,7 +10653,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10631,10 +10662,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>104</v>
@@ -10655,22 +10686,22 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10703,19 +10734,19 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>26</v>
@@ -10723,7 +10754,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10738,7 +10769,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10747,13 +10778,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="I284" s="7">
         <v>81</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10771,22 +10802,22 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10804,7 +10835,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10819,7 +10850,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10837,7 +10868,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -10849,10 +10880,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10885,7 +10916,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10905,7 +10936,7 @@
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -10920,7 +10951,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10932,7 +10963,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>60</v>
@@ -10940,7 +10971,7 @@
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -10955,7 +10986,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10967,7 +10998,7 @@
         <v>298</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>83</v>
@@ -10975,7 +11006,7 @@
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -10990,7 +11021,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11002,10 +11033,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -11023,7 +11054,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11032,17 +11063,21 @@
         <v>21</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>325</v>
-      </c>
-      <c r="K293" s="7"/>
+        <v>327</v>
+      </c>
+      <c t="s" r="K293" s="7">
+        <v>177</v>
+      </c>
       <c r="L293" s="7"/>
-      <c r="M293" s="7"/>
+      <c t="s" r="M293" s="7">
+        <v>403</v>
+      </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
       <c t="s" r="A294" s="6">
@@ -11056,26 +11091,30 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>158</v>
-      </c>
-      <c r="K294" s="7"/>
+        <v>162</v>
+      </c>
+      <c t="s" r="K294" s="7">
+        <v>290</v>
+      </c>
       <c r="L294" s="7"/>
-      <c r="M294" s="7"/>
+      <c t="s" r="M294" s="7">
+        <v>188</v>
+      </c>
     </row>
     <row r="295" ht="15" customHeight="1">
       <c r="A295" s="6"/>
@@ -11104,7 +11143,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11119,12 +11158,12 @@
         <v>285</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11139,7 +11178,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -11151,15 +11190,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11174,7 +11213,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -11183,13 +11222,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -11209,13 +11248,13 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>21</v>
@@ -11224,11 +11263,13 @@
         <v>96</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
-      <c r="M299" s="7"/>
+      <c t="s" r="M299" s="7">
+        <v>405</v>
+      </c>
     </row>
     <row r="300" ht="15" customHeight="1">
       <c t="s" r="A300" s="6">
@@ -11242,7 +11283,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11251,10 +11292,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c t="s" r="J300" s="7">
         <v>84</v>
@@ -11275,19 +11316,19 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>31</v>
@@ -11323,7 +11364,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11335,15 +11376,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -11358,7 +11399,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11367,18 +11408,18 @@
         <v>58</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11393,22 +11434,22 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -11426,7 +11467,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11435,10 +11476,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>404</v>
+        <v>117</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>104</v>
@@ -11459,22 +11500,22 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11507,7 +11548,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11519,15 +11560,15 @@
         <v>95</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11542,7 +11583,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11562,7 +11603,7 @@
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11577,7 +11618,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11586,18 +11627,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11612,22 +11653,22 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>404</v>
+        <v>117</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11660,7 +11701,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11669,18 +11710,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -11695,13 +11736,13 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>21</v>
@@ -11715,7 +11756,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -11730,7 +11771,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11739,18 +11780,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c t="s" r="I316" s="7">
         <v>55</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11765,13 +11806,13 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>21</v>
@@ -11780,12 +11821,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11800,7 +11841,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11809,13 +11850,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11833,13 +11874,13 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>21</v>
@@ -11848,7 +11889,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11881,7 +11922,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11893,7 +11934,7 @@
         <v>70</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>18</v>
@@ -11901,7 +11942,7 @@
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -11916,7 +11957,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11931,12 +11972,12 @@
         <v>93</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -11951,7 +11992,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11963,7 +12004,7 @@
         <v>80</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>38</v>
@@ -11971,7 +12012,7 @@
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -11986,7 +12027,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -12001,14 +12042,14 @@
         <v>62</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c t="s" r="K324" s="7">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12023,7 +12064,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12035,17 +12076,17 @@
         <v>50</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>101</v>
       </c>
       <c t="s" r="K325" s="7">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12060,7 +12101,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -12072,17 +12113,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>33</v>
       </c>
       <c t="s" r="K326" s="7">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12112,7 +12153,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -12124,15 +12165,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12147,7 +12188,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12159,10 +12200,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -12182,7 +12223,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12194,15 +12235,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12217,7 +12258,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -12229,15 +12270,15 @@
         <v>80</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>427</v>
+        <v>301</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12252,7 +12293,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12261,13 +12302,13 @@
         <v>80</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -12285,22 +12326,22 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>80</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>174</v>
+        <v>119</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -12318,7 +12359,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -12330,10 +12371,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12366,7 +12407,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -12381,12 +12422,12 @@
         <v>68</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -12401,7 +12442,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12416,12 +12457,12 @@
         <v>285</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12436,7 +12477,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12456,7 +12497,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12471,7 +12512,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12483,15 +12524,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12506,7 +12547,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12515,18 +12556,18 @@
         <v>58</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12541,13 +12582,13 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>58</v>
@@ -12556,7 +12597,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12589,7 +12630,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12598,10 +12639,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>107</v>
@@ -12609,7 +12650,7 @@
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12624,13 +12665,13 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>21</v>
@@ -12644,7 +12685,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12659,7 +12700,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12674,12 +12715,12 @@
         <v>73</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12694,7 +12735,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12716,7 +12757,7 @@
       </c>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -12731,7 +12772,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12740,18 +12781,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="I347" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -12766,13 +12807,13 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>21</v>
@@ -12781,7 +12822,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12799,7 +12840,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12808,13 +12849,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12832,19 +12873,19 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>71</v>
@@ -12880,7 +12921,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12889,7 +12930,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="I352" s="7">
         <v>109</v>
@@ -12900,7 +12941,7 @@
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -12915,19 +12956,19 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>75</v>
@@ -12935,7 +12976,7 @@
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -12950,7 +12991,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12962,10 +13003,10 @@
         <v>70</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12985,7 +13026,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -13000,12 +13041,12 @@
         <v>40</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -13020,7 +13061,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -13029,13 +13070,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -13053,22 +13094,22 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -13101,7 +13142,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13110,10 +13151,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>285</v>
@@ -13121,7 +13162,7 @@
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13136,19 +13177,19 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>73</v>
@@ -13156,7 +13197,7 @@
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13171,7 +13212,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13183,15 +13224,15 @@
         <v>70</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13206,7 +13247,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13218,15 +13259,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13241,7 +13282,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13250,20 +13291,20 @@
         <v>21</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="I363" s="7">
         <v>94</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c t="s" r="K363" s="7">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13278,13 +13319,13 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>21</v>
@@ -13293,14 +13334,14 @@
         <v>96</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c t="s" r="K364" s="7">
         <v>63</v>
       </c>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13315,7 +13356,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13324,13 +13365,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -13348,22 +13389,22 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I366" s="7">
+        <v>242</v>
+      </c>
+      <c t="s" r="J366" s="7">
         <v>239</v>
-      </c>
-      <c t="s" r="J366" s="7">
-        <v>236</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -13381,7 +13422,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -13393,10 +13434,10 @@
         <v>90</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -13429,7 +13470,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -13438,18 +13479,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13464,13 +13505,13 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>50</v>
@@ -13484,7 +13525,7 @@
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13499,7 +13540,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -13511,7 +13552,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>78</v>
@@ -13519,7 +13560,7 @@
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13534,7 +13575,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13549,7 +13590,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c t="s" r="K372" s="7">
         <v>79</v>
@@ -13571,7 +13612,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -13583,10 +13624,10 @@
         <v>298</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13604,7 +13645,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -13616,10 +13657,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13637,7 +13678,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -13646,13 +13687,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13670,19 +13711,19 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>106</v>
@@ -13718,7 +13759,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13727,10 +13768,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>78</v>
@@ -13738,7 +13779,7 @@
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -13753,13 +13794,13 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>50</v>
@@ -13768,12 +13809,12 @@
         <v>60</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -13788,7 +13829,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -13797,13 +13838,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13821,22 +13862,22 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13869,7 +13910,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13884,12 +13925,12 @@
         <v>48</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -13904,7 +13945,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13937,7 +13978,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13952,7 +13993,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>466</v>
+        <v>403</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13970,7 +14011,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13985,7 +14026,7 @@
         <v>290</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>280</v>
+        <v>120</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -14018,7 +14059,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -14030,7 +14071,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>53</v>
@@ -14038,7 +14079,7 @@
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14053,7 +14094,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -14062,7 +14103,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="I389" s="7">
         <v>19</v>
@@ -14073,7 +14114,7 @@
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14088,29 +14129,29 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="K390" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14125,7 +14166,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -14134,13 +14175,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c t="s" r="I391" s="7">
         <v>28</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -14158,22 +14199,22 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -14206,7 +14247,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -14218,15 +14259,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14241,7 +14282,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14253,7 +14294,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>94</v>
@@ -14261,7 +14302,7 @@
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14276,7 +14317,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14288,17 +14329,17 @@
         <v>58</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>19</v>
       </c>
       <c t="s" r="K396" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14313,7 +14354,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -14322,13 +14363,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -14346,19 +14387,19 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>291</v>
@@ -14379,7 +14420,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -14391,7 +14432,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>34</v>
@@ -14427,7 +14468,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14436,18 +14477,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14462,19 +14503,19 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>41</v>
@@ -14482,7 +14523,7 @@
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14497,7 +14538,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -14509,10 +14550,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -14530,7 +14571,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -14542,7 +14583,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>291</v>
@@ -14563,7 +14604,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14575,7 +14616,7 @@
         <v>90</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>109</v>
@@ -14611,7 +14652,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14620,18 +14661,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="I407" s="7">
         <v>34</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14646,27 +14687,27 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="H408" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14681,7 +14722,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -14690,10 +14731,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>94</v>
@@ -14701,7 +14742,7 @@
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -14716,29 +14757,29 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c t="s" r="K410" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -14753,7 +14794,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14765,10 +14806,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="K411" s="7">
         <v>63</v>
@@ -14790,7 +14831,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14805,7 +14846,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14823,7 +14864,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -14835,10 +14876,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>174</v>
+        <v>119</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14856,7 +14897,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14868,10 +14909,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14904,7 +14945,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14916,15 +14957,15 @@
         <v>298</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -14939,7 +14980,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14951,15 +14992,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -14974,7 +15015,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14983,18 +15024,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -15009,27 +15050,27 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -15044,7 +15085,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -15053,10 +15094,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c t="s" r="J420" s="7">
         <v>67</v>
@@ -15077,19 +15118,19 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c t="s" r="H421" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c t="s" r="J421" s="7">
         <v>294</v>
@@ -15125,13 +15166,13 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>50</v>
@@ -15140,7 +15181,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -15160,7 +15201,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -15175,12 +15216,12 @@
         <v>62</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
       <c t="s" r="M424" s="7">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1">
@@ -15195,7 +15236,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -15207,7 +15248,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>31</v>
@@ -15228,7 +15269,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -15237,13 +15278,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H426" s="8">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -15276,7 +15317,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -15285,18 +15326,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="I428" s="7">
         <v>109</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
       <c t="s" r="M428" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -15311,22 +15352,22 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G429" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="H429" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -15346,7 +15387,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
@@ -15358,14 +15399,16 @@
         <v>21</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
-      <c r="M430" s="7"/>
+      <c t="s" r="M430" s="7">
+        <v>493</v>
+      </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
       <c t="s" r="A431" s="6">
@@ -15379,7 +15422,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F431" s="7">
         <v>321</v>
@@ -15391,10 +15434,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -15412,7 +15455,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
@@ -15424,10 +15467,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -15445,7 +15488,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
@@ -15457,7 +15500,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c t="s" r="J433" s="7">
         <v>32</v>
@@ -15478,7 +15521,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -15490,10 +15533,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -15526,7 +15569,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="F436" s="7">
         <v>320</v>
@@ -15535,18 +15578,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H436" s="8">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -15561,13 +15604,13 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="F437" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G437" s="8">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="H437" s="8">
         <v>21</v>
@@ -15576,12 +15619,12 @@
         <v>285</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -15596,7 +15639,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="F438" s="7">
         <v>320</v>
@@ -15608,15 +15651,15 @@
         <v>298</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
       <c t="s" r="M438" s="7">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
@@ -15631,7 +15674,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="F439" s="7">
         <v>320</v>
@@ -15643,15 +15686,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -15666,7 +15709,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="F440" s="7">
         <v>320</v>
@@ -15678,7 +15721,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="J440" s="7">
         <v>28</v>
@@ -15686,7 +15729,7 @@
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -15701,7 +15744,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="F441" s="7">
         <v>320</v>
@@ -15713,10 +15756,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -15749,7 +15792,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
@@ -15758,7 +15801,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c t="s" r="I443" s="7">
         <v>111</v>
@@ -15769,7 +15812,7 @@
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -15784,22 +15827,22 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="F444" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c t="s" r="H444" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15832,7 +15875,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
@@ -15844,15 +15887,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -15867,7 +15910,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
@@ -15876,18 +15919,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H447" s="8">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c t="s" r="I447" s="7">
         <v>78</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -15902,22 +15945,22 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="F448" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G448" s="8">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c t="s" r="H448" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15950,7 +15993,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="F450" s="7">
         <v>330</v>
@@ -15962,10 +16005,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15983,7 +16026,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="F451" s="7">
         <v>330</v>
@@ -15992,13 +16035,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H451" s="8">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -16031,7 +16074,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="F453" s="7">
         <v>330</v>
@@ -16040,18 +16083,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H453" s="8">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c t="s" r="I453" s="7">
         <v>38</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
       <c t="s" r="M453" s="7">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
@@ -16066,22 +16109,22 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G454" s="8">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c t="s" r="H454" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -16114,7 +16157,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F456" s="7">
         <v>330</v>
@@ -16129,12 +16172,12 @@
         <v>23</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
       <c t="s" r="M456" s="7">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="457" ht="14.25" customHeight="1">
@@ -16164,7 +16207,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F458" s="7">
         <v>330</v>
@@ -16176,15 +16219,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
       <c t="s" r="M458" s="7">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="459" ht="14.25" customHeight="1">
@@ -16199,7 +16242,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
@@ -16211,15 +16254,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
       <c t="s" r="M459" s="7">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="460" ht="15" customHeight="1">
@@ -16234,7 +16277,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F460" s="7">
         <v>330</v>
@@ -16246,10 +16289,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -16282,32 +16325,32 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="F462" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G462" s="8">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c t="s" r="H462" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I462" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c t="s" r="J462" s="7">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
       <c t="s" r="M462" s="7">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="463" ht="15.75" customHeight="1">
       <c t="s" r="A463" s="9">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B463" s="9"/>
       <c r="C463" s="9"/>
@@ -16327,7 +16370,7 @@
     <row r="464" ht="65.25" customHeight="1"/>
     <row r="465" ht="17.25" customHeight="1">
       <c t="s" r="A465" s="10">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B465" s="10"/>
       <c r="C465" s="10"/>
@@ -16340,7 +16383,7 @@
       <c r="J465" s="10"/>
       <c r="K465" s="10"/>
       <c t="s" r="L465" s="11">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="M465" s="11"/>
       <c r="N465" s="11"/>

--- a/Data/FlightPlan/FPL_27SEP26.xlsx
+++ b/Data/FlightPlan/FPL_27SEP26.xlsx
@@ -419,6 +419,9 @@
     <t>01:10</t>
   </si>
   <si>
+    <t>01:23</t>
+  </si>
+  <si>
     <t>VN-A524</t>
   </si>
   <si>
@@ -521,261 +524,264 @@
     <t>16:55</t>
   </si>
   <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>06:32</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>10:44</t>
+  </si>
+  <si>
+    <t>12:44</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>15:57</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>18:28</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>11:14</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>13:14</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>15:58</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>18:49</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>07:51</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>09:23</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>13:46</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>15:09</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>15:07</t>
+  </si>
+  <si>
+    <t>17:33</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>18:58</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>09:04</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>17:43</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
     <t>18:35</t>
   </si>
   <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>06:32</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>10:44</t>
-  </si>
-  <si>
-    <t>12:44</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>15:57</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>18:28</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>11:14</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>13:14</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>15:58</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>18:49</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>07:51</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>09:23</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>13:46</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>15:09</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>15:07</t>
-  </si>
-  <si>
-    <t>17:33</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>09:04</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>17:43</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
     <t>VN-A553</t>
   </si>
   <si>
@@ -836,6 +842,9 @@
     <t>15:29</t>
   </si>
   <si>
+    <t>19:16</t>
+  </si>
+  <si>
     <t>BQS</t>
   </si>
   <si>
@@ -854,7 +863,7 @@
     <t>17:20</t>
   </si>
   <si>
-    <t>20:04</t>
+    <t>20:13</t>
   </si>
   <si>
     <t>08:00</t>
@@ -887,6 +896,9 @@
     <t>10:35</t>
   </si>
   <si>
+    <t>19:32</t>
+  </si>
+  <si>
     <t>VN-A629</t>
   </si>
   <si>
@@ -902,9 +914,6 @@
     <t>17:55</t>
   </si>
   <si>
-    <t>17:56</t>
-  </si>
-  <si>
     <t>18:45</t>
   </si>
   <si>
@@ -1004,7 +1013,7 @@
     <t>13:47</t>
   </si>
   <si>
-    <t>19:11</t>
+    <t>19:13</t>
   </si>
   <si>
     <t>VN-A635</t>
@@ -1052,270 +1061,270 @@
     <t>16:33</t>
   </si>
   <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>11:01</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>15:39</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:12</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>10:57</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>15:34</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>10:59</t>
+  </si>
+  <si>
+    <t>13:36</t>
+  </si>
+  <si>
+    <t>15:53</t>
+  </si>
+  <si>
+    <t>17:49</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>07:58</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>18:46</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>19:17</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>09:03</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:12</t>
+  </si>
+  <si>
+    <t>15:33</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>19:02</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>18:02</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>14:57</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>16:53</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
     <t>20:15</t>
   </si>
   <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>10:07</t>
+  </si>
+  <si>
+    <t>12:34</t>
+  </si>
+  <si>
+    <t>15:01</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>17:07</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>11:21</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>00:36</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>16:51</t>
+  </si>
+  <si>
+    <t>18:54</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>10:49</t>
+  </si>
+  <si>
+    <t>16:08</t>
+  </si>
+  <si>
+    <t>18:03</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>10:19</t>
+  </si>
+  <si>
+    <t>19:18</t>
+  </si>
+  <si>
     <t>00:45</t>
   </si>
   <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>11:01</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>15:39</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:12</t>
-  </si>
-  <si>
-    <t>09:01</t>
-  </si>
-  <si>
-    <t>10:57</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>12:46</t>
-  </si>
-  <si>
-    <t>15:34</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>10:59</t>
-  </si>
-  <si>
-    <t>13:36</t>
-  </si>
-  <si>
-    <t>15:53</t>
-  </si>
-  <si>
-    <t>17:49</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>07:58</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>18:46</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>19:17</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>09:03</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:12</t>
-  </si>
-  <si>
-    <t>15:33</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>19:02</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>09:07</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>18:02</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>14:57</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>16:53</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>10:07</t>
-  </si>
-  <si>
-    <t>12:34</t>
-  </si>
-  <si>
-    <t>15:01</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>17:07</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>11:21</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>00:36</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>16:51</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>10:49</t>
-  </si>
-  <si>
-    <t>16:08</t>
-  </si>
-  <si>
-    <t>18:03</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>18:21</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>10:19</t>
-  </si>
-  <si>
-    <t>19:18</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
     <t>VN-A663</t>
   </si>
   <si>
@@ -1439,6 +1448,9 @@
     <t>16:46</t>
   </si>
   <si>
+    <t>19:29</t>
+  </si>
+  <si>
     <t>VN-A674</t>
   </si>
   <si>
@@ -1469,6 +1481,9 @@
     <t>09:58</t>
   </si>
   <si>
+    <t>19:06</t>
+  </si>
+  <si>
     <t>01:15</t>
   </si>
   <si>
@@ -1592,6 +1607,9 @@
     <t>12:14</t>
   </si>
   <si>
+    <t>19:14</t>
+  </si>
+  <si>
     <t>VN-A810</t>
   </si>
   <si>
@@ -1652,7 +1670,7 @@
     <t>Total Record(s): 381</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 27, 2026 17:19</t>
+    <t xml:space="preserve">Generated on  Sep 27, 2026 17:49</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3582,7 +3600,9 @@
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
+      <c t="s" r="M49" s="7">
+        <v>136</v>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="6"/>
@@ -3611,7 +3631,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3623,7 +3643,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J51" s="7">
         <v>130</v>
@@ -3631,7 +3651,7 @@
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
       <c t="s" r="M51" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -3646,7 +3666,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3661,12 +3681,12 @@
         <v>26</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c t="s" r="M52" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
@@ -3681,7 +3701,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3696,14 +3716,14 @@
         <v>133</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="K53" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L53" s="7"/>
       <c t="s" r="M53" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
@@ -3718,7 +3738,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3762,17 +3782,17 @@
         <v>3524</v>
       </c>
       <c t="s" r="C56" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="H56" s="8">
         <v>51</v>
@@ -3781,12 +3801,12 @@
         <v>20</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
       <c t="s" r="M56" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -3797,11 +3817,11 @@
         <v>3524</v>
       </c>
       <c t="s" r="C57" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3813,15 +3833,15 @@
         <v>72</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
       <c t="s" r="M57" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
@@ -3836,7 +3856,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3851,7 +3871,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3884,7 +3904,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3896,15 +3916,15 @@
         <v>129</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c t="s" r="M60" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -3919,7 +3939,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3931,15 +3951,15 @@
         <v>51</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
       <c t="s" r="M61" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -3954,7 +3974,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3966,10 +3986,10 @@
         <v>110</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -4002,7 +4022,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -4022,7 +4042,7 @@
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c t="s" r="M64" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
@@ -4037,7 +4057,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -4052,12 +4072,12 @@
         <v>93</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
       <c t="s" r="M65" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -4072,7 +4092,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -4084,7 +4104,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J66" s="7">
         <v>96</v>
@@ -4092,7 +4112,7 @@
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c t="s" r="M66" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -4107,7 +4127,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -4119,17 +4139,17 @@
         <v>51</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="K67" s="7">
         <v>81</v>
       </c>
       <c r="L67" s="7"/>
       <c t="s" r="M67" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
@@ -4144,7 +4164,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -4159,14 +4179,14 @@
         <v>98</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="K68" s="7">
         <v>83</v>
       </c>
       <c r="L68" s="7"/>
       <c t="s" r="M68" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -4181,7 +4201,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -4193,7 +4213,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J69" s="7">
         <v>29</v>
@@ -4203,7 +4223,7 @@
       </c>
       <c r="L69" s="7"/>
       <c t="s" r="M69" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
@@ -4218,7 +4238,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -4230,7 +4250,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J70" s="7">
         <v>125</v>
@@ -4251,7 +4271,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -4263,10 +4283,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -4299,7 +4319,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -4314,12 +4334,12 @@
         <v>73</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c t="s" r="M73" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -4334,7 +4354,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -4343,10 +4363,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J74" s="7">
         <v>38</v>
@@ -4354,7 +4374,7 @@
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -4369,19 +4389,19 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="H75" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J75" s="7">
         <v>20</v>
@@ -4389,7 +4409,7 @@
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4404,7 +4424,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4424,7 +4444,7 @@
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4439,7 +4459,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4448,10 +4468,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H77" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J77" s="7">
         <v>85</v>
@@ -4459,7 +4479,7 @@
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c t="s" r="M77" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -4474,19 +4494,19 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="H78" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J78" s="7">
         <v>29</v>
@@ -4494,7 +4514,7 @@
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -4509,7 +4529,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4521,7 +4541,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c t="s" r="J79" s="7">
         <v>126</v>
@@ -4542,7 +4562,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4605,7 +4625,7 @@
         <v>192</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4707,7 +4727,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J85" s="7">
         <v>196</v>
@@ -4862,7 +4882,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>205</v>
@@ -4897,7 +4917,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>207</v>
@@ -4950,7 +4970,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -5095,7 +5115,7 @@
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>219</v>
+        <v>195</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -5306,7 +5326,7 @@
         <v>230</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J104" s="7">
         <v>199</v>
@@ -5564,17 +5584,17 @@
         <v>51</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="K112" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5604,7 +5624,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5616,15 +5636,15 @@
         <v>72</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c t="s" r="M114" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -5639,7 +5659,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5674,7 +5694,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5696,7 +5716,7 @@
       </c>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5711,7 +5731,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5726,14 +5746,14 @@
         <v>26</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="K117" s="7">
         <v>98</v>
       </c>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5748,7 +5768,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5760,10 +5780,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5796,7 +5816,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5814,7 +5834,7 @@
         <v>132</v>
       </c>
       <c t="s" r="K120" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
@@ -5833,7 +5853,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5845,15 +5865,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -5868,7 +5888,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5880,7 +5900,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>45</v>
@@ -5905,7 +5925,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5917,7 +5937,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>196</v>
@@ -5927,7 +5947,7 @@
       </c>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -5957,7 +5977,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5969,7 +5989,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J125" s="7">
         <v>39</v>
@@ -5994,7 +6014,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -6006,7 +6026,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>170</v>
+        <v>256</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>106</v>
@@ -6042,7 +6062,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -6077,7 +6097,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6089,17 +6109,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="K129" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -6114,7 +6134,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -6126,17 +6146,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="K130" s="7">
         <v>69</v>
       </c>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -6162,11 +6182,11 @@
         <v>7621</v>
       </c>
       <c t="s" r="C132" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6181,12 +6201,12 @@
         <v>75</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -6201,7 +6221,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6210,7 +6230,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="I133" s="7">
         <v>205</v>
@@ -6221,7 +6241,7 @@
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -6236,19 +6256,19 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>231</v>
@@ -6269,7 +6289,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6281,7 +6301,7 @@
         <v>92</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>76</v>
@@ -6317,22 +6337,22 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -6352,7 +6372,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6367,12 +6387,12 @@
         <v>81</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6383,11 +6403,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C139" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6399,14 +6419,16 @@
         <v>51</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>105</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
-      <c r="M139" s="7"/>
+      <c t="s" r="M139" s="7">
+        <v>277</v>
+      </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c t="s" r="A140" s="6">
@@ -6416,11 +6438,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6429,13 +6451,13 @@
         <v>51</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="I140" s="7">
         <v>104</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -6468,7 +6490,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6480,15 +6502,15 @@
         <v>51</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6503,7 +6525,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6512,7 +6534,7 @@
         <v>51</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="I143" s="7">
         <v>61</v>
@@ -6523,7 +6545,7 @@
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6538,13 +6560,13 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>51</v>
@@ -6558,7 +6580,7 @@
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6573,7 +6595,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6585,10 +6607,10 @@
         <v>129</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6621,7 +6643,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6630,10 +6652,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>80</v>
@@ -6656,13 +6678,13 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>21</v>
@@ -6676,7 +6698,7 @@
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6691,7 +6713,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6700,10 +6722,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>105</v>
@@ -6724,22 +6746,22 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6757,7 +6779,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6769,7 +6791,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>201</v>
@@ -6805,27 +6827,27 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6840,7 +6862,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6849,17 +6871,19 @@
         <v>21</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>32</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
-      <c r="M154" s="7"/>
+      <c t="s" r="M154" s="7">
+        <v>295</v>
+      </c>
     </row>
     <row r="155" ht="15" customHeight="1">
       <c t="s" r="A155" s="6">
@@ -6873,13 +6897,13 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>21</v>
@@ -6906,7 +6930,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6915,7 +6939,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="I156" s="7">
         <v>111</v>
@@ -6954,7 +6978,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6966,7 +6990,7 @@
         <v>214</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>79</v>
@@ -6974,7 +6998,7 @@
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6989,7 +7013,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -7004,7 +7028,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -7024,7 +7048,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7039,12 +7063,12 @@
         <v>100</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>297</v>
+        <v>219</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7059,7 +7083,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -7071,10 +7095,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -7092,7 +7116,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -7125,7 +7149,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -7137,10 +7161,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -7173,7 +7197,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7182,10 +7206,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>57</v>
@@ -7193,7 +7217,7 @@
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7208,13 +7232,13 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>21</v>
@@ -7223,12 +7247,12 @@
         <v>193</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7243,7 +7267,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7252,7 +7276,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c t="s" r="I167" s="7">
         <v>87</v>
@@ -7263,7 +7287,7 @@
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>188</v>
+        <v>171</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -7278,13 +7302,13 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>21</v>
@@ -7293,7 +7317,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -7311,7 +7335,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7323,10 +7347,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -7359,7 +7383,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7368,10 +7392,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>93</v>
@@ -7379,7 +7403,7 @@
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7394,27 +7418,27 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -7429,7 +7453,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7438,18 +7462,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7464,27 +7488,27 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7499,7 +7523,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7511,7 +7535,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>27</v>
@@ -7519,7 +7543,7 @@
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7534,7 +7558,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7549,12 +7573,12 @@
         <v>87</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7569,7 +7593,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7578,13 +7602,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="I177" s="7">
         <v>123</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7602,22 +7626,22 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7650,7 +7674,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7659,18 +7683,18 @@
         <v>51</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="I180" s="7">
         <v>234</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7685,13 +7709,13 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>51</v>
@@ -7700,12 +7724,12 @@
         <v>79</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7720,7 +7744,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7729,7 +7753,7 @@
         <v>51</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="I182" s="7">
         <v>41</v>
@@ -7738,11 +7762,11 @@
         <v>67</v>
       </c>
       <c t="s" r="K182" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7757,19 +7781,19 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>89</v>
@@ -7790,7 +7814,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7805,7 +7829,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7838,7 +7862,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7847,18 +7871,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -7873,22 +7897,22 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7908,7 +7932,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7920,15 +7944,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7943,7 +7967,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7955,15 +7979,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -7978,7 +8002,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7993,12 +8017,12 @@
         <v>218</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -8013,7 +8037,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8025,7 +8049,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J191" s="7">
         <v>198</v>
@@ -8046,7 +8070,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -8058,7 +8082,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>135</v>
@@ -8094,7 +8118,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8106,7 +8130,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>56</v>
@@ -8114,7 +8138,7 @@
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -8129,7 +8153,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8141,7 +8165,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>22</v>
@@ -8149,7 +8173,7 @@
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8164,7 +8188,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8176,7 +8200,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>98</v>
@@ -8184,7 +8208,7 @@
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8199,7 +8223,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8208,7 +8232,7 @@
         <v>51</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="I197" s="7">
         <v>85</v>
@@ -8219,7 +8243,7 @@
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8234,13 +8258,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>51</v>
@@ -8249,7 +8273,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -8267,7 +8291,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8279,17 +8303,17 @@
         <v>59</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c t="s" r="K199" s="7">
         <v>197</v>
       </c>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8304,7 +8328,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8316,7 +8340,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>33</v>
@@ -8356,7 +8380,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8376,7 +8400,7 @@
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8391,7 +8415,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8403,7 +8427,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>216</v>
@@ -8411,7 +8435,7 @@
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8426,7 +8450,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8441,14 +8465,14 @@
         <v>23</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c t="s" r="K204" s="7">
         <v>83</v>
       </c>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8463,7 +8487,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8475,28 +8499,30 @@
         <v>21</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>103</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
-      <c r="M205" s="7"/>
+      <c t="s" r="M205" s="7">
+        <v>208</v>
+      </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
       <c t="s" r="A206" s="6">
         <v>13</v>
       </c>
       <c r="B206" s="7">
-        <v>1282</v>
+        <v>3900</v>
       </c>
       <c t="s" r="C206" s="7">
         <v>14</v>
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8505,13 +8531,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>347</v>
+        <v>124</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8519,32 +8545,32 @@
     </row>
     <row r="207" ht="14.25" customHeight="1">
       <c t="s" r="A207" s="6">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="B207" s="7">
-        <v>1283</v>
+        <v>3901</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c t="s" r="H207" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>172</v>
+        <v>351</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8577,7 +8603,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8589,10 +8615,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -8612,7 +8638,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8624,7 +8650,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>20</v>
@@ -8632,7 +8658,7 @@
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8647,7 +8673,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8667,7 +8693,7 @@
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8682,7 +8708,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8700,11 +8726,11 @@
         <v>41</v>
       </c>
       <c t="s" r="K212" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8719,7 +8745,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8734,7 +8760,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8754,7 +8780,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8802,7 +8828,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8814,7 +8840,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>234</v>
@@ -8822,7 +8848,7 @@
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8837,7 +8863,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8849,15 +8875,15 @@
         <v>51</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8872,7 +8898,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8881,18 +8907,18 @@
         <v>51</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -8907,13 +8933,13 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>51</v>
@@ -8922,14 +8948,14 @@
         <v>94</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="K219" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -8944,7 +8970,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8962,11 +8988,11 @@
         <v>83</v>
       </c>
       <c t="s" r="K220" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -8981,7 +9007,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -9018,7 +9044,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -9030,10 +9056,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -9051,7 +9077,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9063,10 +9089,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -9099,7 +9125,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9108,10 +9134,10 @@
         <v>51</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>23</v>
@@ -9134,13 +9160,13 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>51</v>
@@ -9154,7 +9180,7 @@
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9169,7 +9195,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9181,13 +9207,13 @@
         <v>21</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c t="s" r="K227" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
@@ -9206,7 +9232,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9215,13 +9241,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -9239,22 +9265,22 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -9287,7 +9313,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9299,10 +9325,10 @@
         <v>82</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -9322,7 +9348,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9342,7 +9368,7 @@
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9372,7 +9398,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9392,7 +9418,7 @@
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9407,7 +9433,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9419,7 +9445,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>61</v>
@@ -9427,7 +9453,7 @@
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9442,7 +9468,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9454,7 +9480,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>100</v>
@@ -9462,7 +9488,7 @@
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9477,7 +9503,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9492,12 +9518,12 @@
         <v>28</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -9512,7 +9538,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9545,7 +9571,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9593,7 +9619,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9613,7 +9639,7 @@
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9628,7 +9654,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9637,7 +9663,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="I242" s="7">
         <v>235</v>
@@ -9648,7 +9674,7 @@
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9663,13 +9689,13 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>72</v>
@@ -9678,12 +9704,12 @@
         <v>81</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9698,7 +9724,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9707,7 +9733,7 @@
         <v>72</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>100</v>
@@ -9718,7 +9744,7 @@
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9733,13 +9759,13 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>21</v>
@@ -9781,7 +9807,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9816,7 +9842,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9825,7 +9851,7 @@
         <v>51</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c t="s" r="I248" s="7">
         <v>131</v>
@@ -9836,7 +9862,7 @@
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9851,22 +9877,22 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9884,7 +9910,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9896,10 +9922,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9932,7 +9958,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9947,12 +9973,12 @@
         <v>234</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -9967,7 +9993,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9979,15 +10005,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -10002,7 +10028,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -10017,7 +10043,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -10037,7 +10063,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -10057,7 +10083,7 @@
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -10072,7 +10098,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -10084,15 +10110,15 @@
         <v>72</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -10107,7 +10133,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -10122,7 +10148,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -10155,7 +10181,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -10167,7 +10193,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>236</v>
@@ -10175,7 +10201,7 @@
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10190,7 +10216,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10202,15 +10228,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10225,7 +10251,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10234,7 +10260,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>61</v>
@@ -10245,7 +10271,7 @@
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -10260,22 +10286,22 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -10293,7 +10319,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10308,7 +10334,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -10341,7 +10367,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -10350,18 +10376,18 @@
         <v>59</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="I265" s="7">
         <v>96</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10376,13 +10402,13 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>59</v>
@@ -10391,12 +10417,12 @@
         <v>27</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10426,7 +10452,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -10435,18 +10461,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="I268" s="7">
         <v>74</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10461,19 +10487,19 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>118</v>
@@ -10481,7 +10507,7 @@
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10496,7 +10522,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -10531,7 +10557,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
@@ -10553,7 +10579,7 @@
       </c>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10568,7 +10594,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -10577,13 +10603,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c t="s" r="I272" s="7">
         <v>195</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -10601,22 +10627,22 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>347</v>
+        <v>408</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -10649,7 +10675,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10664,12 +10690,12 @@
         <v>54</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10684,7 +10710,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10704,7 +10730,7 @@
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10719,7 +10745,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10731,15 +10757,15 @@
         <v>52</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -10754,7 +10780,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10766,15 +10792,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10804,7 +10830,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10813,18 +10839,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10839,19 +10865,19 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>40</v>
@@ -10859,7 +10885,7 @@
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10874,7 +10900,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10883,10 +10909,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>111</v>
@@ -10894,7 +10920,7 @@
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -10909,22 +10935,22 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10957,19 +10983,19 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>26</v>
@@ -10977,7 +11003,7 @@
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -10992,7 +11018,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -11012,7 +11038,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -11027,7 +11053,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -11039,14 +11065,16 @@
         <v>51</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
-      <c r="M287" s="7"/>
+      <c t="s" r="M287" s="7">
+        <v>425</v>
+      </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
       <c t="s" r="A288" s="6">
@@ -11060,7 +11088,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -11075,7 +11103,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -11093,7 +11121,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -11108,7 +11136,7 @@
         <v>109</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -11141,7 +11169,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11153,7 +11181,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>77</v>
@@ -11161,7 +11189,7 @@
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11176,7 +11204,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11188,7 +11216,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>61</v>
@@ -11196,7 +11224,7 @@
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11211,7 +11239,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11220,10 +11248,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>85</v>
@@ -11231,7 +11259,7 @@
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11246,27 +11274,27 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11281,7 +11309,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -11290,20 +11318,20 @@
         <v>21</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="I295" s="7">
         <v>207</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>347</v>
+        <v>408</v>
       </c>
       <c t="s" r="K295" s="7">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11318,25 +11346,25 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="K296" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
@@ -11370,7 +11398,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -11382,7 +11410,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>201</v>
@@ -11390,7 +11418,7 @@
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11405,7 +11433,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -11417,15 +11445,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11440,7 +11468,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11449,13 +11477,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c t="s" r="I300" s="7">
         <v>130</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -11475,13 +11503,13 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>21</v>
@@ -11490,7 +11518,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -11510,7 +11538,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -11519,10 +11547,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>86</v>
@@ -11530,7 +11558,7 @@
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>427</v>
+        <v>188</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11545,13 +11573,13 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>21</v>
@@ -11593,7 +11621,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11605,15 +11633,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11628,7 +11656,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11637,18 +11665,18 @@
         <v>59</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="I306" s="7">
         <v>237</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11663,27 +11691,27 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11691,14 +11719,14 @@
         <v>13</v>
       </c>
       <c r="B308" s="7">
-        <v>3900</v>
+        <v>1282</v>
       </c>
       <c t="s" r="C308" s="7">
         <v>14</v>
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11707,13 +11735,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>124</v>
+        <v>408</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -11721,32 +11749,32 @@
     </row>
     <row r="309" ht="14.25" customHeight="1">
       <c t="s" r="A309" s="6">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="B309" s="7">
-        <v>3901</v>
+        <v>1283</v>
       </c>
       <c t="s" r="C309" s="7">
         <v>14</v>
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>433</v>
+        <v>173</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -11779,7 +11807,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11791,15 +11819,15 @@
         <v>97</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11814,7 +11842,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11834,7 +11862,7 @@
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11849,7 +11877,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11858,18 +11886,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11884,13 +11912,13 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>21</v>
@@ -11899,7 +11927,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11932,7 +11960,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11944,15 +11972,15 @@
         <v>194</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11967,7 +11995,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11987,7 +12015,7 @@
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -12002,7 +12030,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -12017,12 +12045,12 @@
         <v>56</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -12037,7 +12065,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -12052,12 +12080,12 @@
         <v>39</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12072,7 +12100,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -12081,18 +12109,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>133</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12107,13 +12135,13 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>21</v>
@@ -12122,7 +12150,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -12155,7 +12183,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -12167,7 +12195,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>18</v>
@@ -12175,7 +12203,7 @@
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12190,7 +12218,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -12205,12 +12233,12 @@
         <v>95</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12225,7 +12253,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12237,7 +12265,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>39</v>
@@ -12245,7 +12273,7 @@
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12260,7 +12288,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -12275,14 +12303,14 @@
         <v>63</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="K326" s="7">
         <v>131</v>
       </c>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12297,7 +12325,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -12309,7 +12337,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>104</v>
@@ -12334,7 +12362,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -12346,10 +12374,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -12382,7 +12410,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12394,15 +12422,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12417,7 +12445,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -12429,10 +12457,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -12452,7 +12480,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12464,15 +12492,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12487,7 +12515,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12499,7 +12527,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>205</v>
@@ -12507,7 +12535,7 @@
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12522,7 +12550,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -12534,7 +12562,7 @@
         <v>194</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>207</v>
@@ -12542,7 +12570,7 @@
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12557,7 +12585,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -12569,7 +12597,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>126</v>
@@ -12590,7 +12618,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -12602,10 +12630,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12638,7 +12666,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12658,7 +12686,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12673,7 +12701,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12685,15 +12713,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12708,7 +12736,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12728,7 +12756,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12743,7 +12771,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12755,15 +12783,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12778,7 +12806,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12790,15 +12818,15 @@
         <v>194</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12813,7 +12841,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12828,12 +12856,12 @@
         <v>27</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12863,7 +12891,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12872,10 +12900,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>114</v>
@@ -12883,7 +12911,7 @@
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12898,13 +12926,13 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>21</v>
@@ -12918,7 +12946,7 @@
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -12933,7 +12961,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12948,12 +12976,12 @@
         <v>75</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -12968,7 +12996,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12990,7 +13018,7 @@
       </c>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -13005,7 +13033,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -13020,12 +13048,12 @@
         <v>41</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -13040,7 +13068,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -13055,12 +13083,12 @@
         <v>66</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13075,7 +13103,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -13084,13 +13112,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c t="s" r="I351" s="7">
         <v>229</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -13108,19 +13136,19 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>73</v>
@@ -13156,7 +13184,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -13176,7 +13204,7 @@
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13191,7 +13219,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -13203,7 +13231,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>77</v>
@@ -13211,7 +13239,7 @@
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -13226,7 +13254,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -13241,12 +13269,12 @@
         <v>203</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -13261,7 +13289,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -13276,12 +13304,12 @@
         <v>41</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13296,7 +13324,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -13305,17 +13333,19 @@
         <v>51</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>105</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
-      <c r="M358" s="7"/>
+      <c t="s" r="M358" s="7">
+        <v>479</v>
+      </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
       <c t="s" r="A359" s="6">
@@ -13329,22 +13359,22 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -13377,7 +13407,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13386,18 +13416,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13412,19 +13442,19 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>75</v>
@@ -13432,7 +13462,7 @@
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13447,7 +13477,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13459,15 +13489,15 @@
         <v>72</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13482,7 +13512,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13494,15 +13524,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13517,7 +13547,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13526,20 +13556,20 @@
         <v>21</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="I365" s="7">
         <v>96</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="K365" s="7">
         <v>130</v>
       </c>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13554,13 +13584,13 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>21</v>
@@ -13569,14 +13599,14 @@
         <v>98</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c t="s" r="K366" s="7">
         <v>64</v>
       </c>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13591,7 +13621,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -13600,20 +13630,20 @@
         <v>21</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c t="s" r="K367" s="7">
-        <v>170</v>
+        <v>256</v>
       </c>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13628,29 +13658,29 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>106</v>
       </c>
       <c t="s" r="K368" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13665,7 +13695,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13677,10 +13707,10 @@
         <v>92</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -13713,7 +13743,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -13722,18 +13752,18 @@
         <v>51</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13748,13 +13778,13 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>51</v>
@@ -13768,7 +13798,7 @@
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -13783,7 +13813,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -13795,7 +13825,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>80</v>
@@ -13818,7 +13848,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -13855,7 +13885,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -13864,18 +13894,18 @@
         <v>51</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="I375" s="7">
         <v>205</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -13890,26 +13920,28 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
-      <c r="M376" s="7"/>
+      <c t="s" r="M376" s="7">
+        <v>490</v>
+      </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
       <c t="s" r="A377" s="6">
@@ -13923,7 +13955,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -13932,13 +13964,13 @@
         <v>51</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>432</v>
+        <v>350</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13956,19 +13988,19 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>432</v>
+        <v>350</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>113</v>
@@ -14004,7 +14036,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -14013,10 +14045,10 @@
         <v>51</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>80</v>
@@ -14024,7 +14056,7 @@
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -14039,13 +14071,13 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>51</v>
@@ -14054,12 +14086,12 @@
         <v>61</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -14074,7 +14106,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -14083,13 +14115,13 @@
         <v>51</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -14107,22 +14139,22 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -14155,7 +14187,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14170,7 +14202,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -14190,7 +14222,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -14210,7 +14242,7 @@
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -14225,7 +14257,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -14240,7 +14272,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -14258,7 +14290,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -14270,7 +14302,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>127</v>
@@ -14306,7 +14338,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -14318,7 +14350,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>54</v>
@@ -14326,7 +14358,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14341,7 +14373,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -14376,7 +14408,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -14388,10 +14420,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c t="s" r="K392" s="7">
         <v>237</v>
@@ -14413,7 +14445,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -14422,7 +14454,7 @@
         <v>51</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c t="s" r="I393" s="7">
         <v>28</v>
@@ -14448,13 +14480,13 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>51</v>
@@ -14463,7 +14495,7 @@
         <v>240</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -14496,7 +14528,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14516,7 +14548,7 @@
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14531,7 +14563,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -14543,7 +14575,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>96</v>
@@ -14551,7 +14583,7 @@
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14566,7 +14598,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14584,11 +14616,11 @@
         <v>19</v>
       </c>
       <c t="s" r="K398" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14603,7 +14635,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -14612,13 +14644,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="I399" s="7">
         <v>207</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -14636,22 +14668,22 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -14669,7 +14701,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14681,7 +14713,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>35</v>
@@ -14717,7 +14749,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -14726,18 +14758,18 @@
         <v>51</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -14752,13 +14784,13 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>51</v>
@@ -14787,7 +14819,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14802,14 +14834,14 @@
         <v>207</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="K405" s="7">
         <v>105</v>
       </c>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -14824,7 +14856,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14836,17 +14868,17 @@
         <v>51</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c t="s" r="K406" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14861,7 +14893,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14873,7 +14905,7 @@
         <v>92</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>116</v>
@@ -14909,7 +14941,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -14918,18 +14950,18 @@
         <v>51</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="I409" s="7">
         <v>35</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -14944,27 +14976,27 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -14979,7 +15011,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14988,10 +15020,10 @@
         <v>51</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>96</v>
@@ -14999,7 +15031,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -15014,29 +15046,29 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>216</v>
       </c>
       <c t="s" r="K412" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15051,7 +15083,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -15066,7 +15098,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c t="s" r="K413" s="7">
         <v>64</v>
@@ -15088,7 +15120,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -15103,14 +15135,14 @@
         <v>67</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="K414" s="7">
-        <v>170</v>
+        <v>256</v>
       </c>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -15125,7 +15157,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -15137,17 +15169,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>126</v>
       </c>
       <c t="s" r="K415" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -15162,7 +15194,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -15180,7 +15212,7 @@
         <v>199</v>
       </c>
       <c t="s" r="K416" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
@@ -15214,7 +15246,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -15223,18 +15255,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -15249,27 +15281,27 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -15284,7 +15316,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -15293,10 +15325,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c t="s" r="J420" s="7">
         <v>216</v>
@@ -15304,7 +15336,7 @@
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -15319,19 +15351,19 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="H421" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J421" s="7">
         <v>123</v>
@@ -15339,7 +15371,7 @@
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -15354,7 +15386,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -15363,10 +15395,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>69</v>
@@ -15387,22 +15419,22 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -15435,7 +15467,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -15450,7 +15482,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -15470,7 +15502,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -15485,12 +15517,12 @@
         <v>63</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -15505,7 +15537,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -15517,14 +15549,16 @@
         <v>51</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>32</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
-      <c r="M427" s="7"/>
+      <c t="s" r="M427" s="7">
+        <v>295</v>
+      </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
       <c t="s" r="A428" s="6">
@@ -15538,7 +15572,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -15550,10 +15584,10 @@
         <v>191</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -15586,7 +15620,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
@@ -15595,18 +15629,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="I430" s="7">
         <v>116</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -15621,19 +15655,19 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="F431" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="H431" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c t="s" r="J431" s="7">
         <v>237</v>
@@ -15656,7 +15690,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
@@ -15668,15 +15702,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>520</v>
+        <v>525</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -15691,7 +15725,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
@@ -15703,14 +15737,16 @@
         <v>51</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
-      <c r="M433" s="7"/>
+      <c t="s" r="M433" s="7">
+        <v>479</v>
+      </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
       <c t="s" r="A434" s="6">
@@ -15724,7 +15760,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -15736,14 +15772,18 @@
         <v>21</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c t="s" r="J434" s="7">
         <v>34</v>
       </c>
-      <c r="K434" s="7"/>
+      <c t="s" r="K434" s="7">
+        <v>395</v>
+      </c>
       <c r="L434" s="7"/>
-      <c r="M434" s="7"/>
+      <c t="s" r="M434" s="7">
+        <v>34</v>
+      </c>
     </row>
     <row r="435" ht="15" customHeight="1">
       <c r="A435" s="6"/>
@@ -15772,7 +15812,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="F436" s="7">
         <v>320</v>
@@ -15781,10 +15821,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H436" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c t="s" r="J436" s="7">
         <v>234</v>
@@ -15792,7 +15832,7 @@
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>523</v>
+        <v>528</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -15807,27 +15847,27 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="F437" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G437" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="H437" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -15842,7 +15882,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="F438" s="7">
         <v>320</v>
@@ -15851,18 +15891,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H438" s="8">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="I438" s="7">
         <v>236</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
       <c t="s" r="M438" s="7">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
@@ -15877,27 +15917,27 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="F439" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G439" s="8">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="H439" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -15912,7 +15952,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="F440" s="7">
         <v>320</v>
@@ -15924,7 +15964,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J440" s="7">
         <v>28</v>
@@ -15932,7 +15972,7 @@
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -15947,7 +15987,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="F441" s="7">
         <v>320</v>
@@ -15959,15 +15999,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
       <c t="s" r="M441" s="7">
-        <v>390</v>
+        <v>532</v>
       </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
@@ -15997,7 +16037,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
@@ -16006,7 +16046,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c t="s" r="I443" s="7">
         <v>118</v>
@@ -16017,7 +16057,7 @@
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -16032,22 +16072,22 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="F444" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c t="s" r="H444" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -16080,7 +16120,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
@@ -16092,15 +16132,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>531</v>
+        <v>537</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -16115,7 +16155,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
@@ -16124,13 +16164,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H447" s="8">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c t="s" r="I447" s="7">
         <v>80</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -16150,13 +16190,13 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="F448" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G448" s="8">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c t="s" r="H448" s="8">
         <v>17</v>
@@ -16165,7 +16205,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -16198,7 +16238,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="F450" s="7">
         <v>330</v>
@@ -16213,7 +16253,7 @@
         <v>236</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -16231,7 +16271,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="F451" s="7">
         <v>330</v>
@@ -16240,13 +16280,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H451" s="8">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -16279,7 +16319,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="F453" s="7">
         <v>330</v>
@@ -16288,18 +16328,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H453" s="8">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c t="s" r="I453" s="7">
         <v>39</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
       <c t="s" r="M453" s="7">
-        <v>537</v>
+        <v>543</v>
       </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
@@ -16314,22 +16354,22 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G454" s="8">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c t="s" r="H454" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -16362,7 +16402,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="F456" s="7">
         <v>330</v>
@@ -16377,12 +16417,12 @@
         <v>23</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
       <c t="s" r="M456" s="7">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="457" ht="14.25" customHeight="1">
@@ -16412,7 +16452,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="F458" s="7">
         <v>330</v>
@@ -16424,15 +16464,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
       <c t="s" r="M458" s="7">
-        <v>541</v>
+        <v>547</v>
       </c>
     </row>
     <row r="459" ht="14.25" customHeight="1">
@@ -16447,7 +16487,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
@@ -16459,15 +16499,15 @@
         <v>51</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
       <c t="s" r="M459" s="7">
-        <v>542</v>
+        <v>548</v>
       </c>
     </row>
     <row r="460" ht="15" customHeight="1">
@@ -16482,7 +16522,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="F460" s="7">
         <v>330</v>
@@ -16494,15 +16534,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
       <c t="s" r="M460" s="7">
-        <v>543</v>
+        <v>549</v>
       </c>
     </row>
     <row r="461" ht="14.25" customHeight="1">
@@ -16532,32 +16572,32 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="F462" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G462" s="8">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c t="s" r="H462" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I462" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="J462" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
       <c t="s" r="M462" s="7">
-        <v>545</v>
+        <v>551</v>
       </c>
     </row>
     <row r="463" ht="15.75" customHeight="1">
       <c t="s" r="A463" s="9">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="B463" s="9"/>
       <c r="C463" s="9"/>
@@ -16577,7 +16617,7 @@
     <row r="464" ht="65.25" customHeight="1"/>
     <row r="465" ht="17.25" customHeight="1">
       <c t="s" r="A465" s="10">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="B465" s="10"/>
       <c r="C465" s="10"/>
@@ -16590,7 +16630,7 @@
       <c r="J465" s="10"/>
       <c r="K465" s="10"/>
       <c t="s" r="L465" s="11">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="M465" s="11"/>
       <c r="N465" s="11"/>
